--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -281,7 +281,7 @@
 con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}se-genetic-evidence:Genetic diagnosis must have at least one evidence.detail referencing a MolGen resource {evidence.exists() and evidence.detail.exists()}</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.GenetischeDiagnose</t>
+    <t>anamneseUndDiagnostik.genetischeDiagnose</t>
   </si>
   <si>
     <t>Event</t>
@@ -730,7 +730,7 @@
 </t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.GenetischeDiagnose.FeststellungsdatumGenDia</t>
+    <t>anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
   </si>
   <si>
     <t>Condition.extension:penetrance</t>
@@ -749,7 +749,7 @@
     <t>Angabe zur Penetranz der genetischen Variante bei dieser Erkrankung</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.GenDiaFehlendePenetranz</t>
+    <t>anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -1911,7 +1911,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Untersuchungsdatum</t>
+    <t>anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1964,7 +1964,7 @@
     <t>closed</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.GenetischeDiagnose.AlterGenDia</t>
+    <t>anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum</t>
@@ -2791,7 +2791,7 @@
 </t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.MethodeDiagnosestellung</t>
+    <t>anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -3221,7 +3221,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="59.1875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="58.50390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="42.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1803,7 +1803,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
